--- a/imports/seller_onboarding/aquatic_exotica_bulk_upload.xlsx
+++ b/imports/seller_onboarding/aquatic_exotica_bulk_upload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CategoryMapping" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SourceAPI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CategoryMapping" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceAPI" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,8 +445,8 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="47" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
@@ -742,12 +742,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Terrarium &amp; Paludarium</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Terrarium &amp; Paludarium</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -7098,12 +7098,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -7997,12 +7997,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -9429,12 +9429,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -10332,12 +10332,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Terrarium &amp; Paludarium|Plants</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Terrarium Moss|Mosses</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Terrarium &amp; Paludarium</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Rare &amp; Exotic|Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Terrarium &amp; Paludarium|Plants</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Terrarium Moss|Mosses</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Moss|Terrarium Moss|Aquatic Plants</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -12476,12 +12476,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants|Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants|Terrarium Plants</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Terrarium &amp; Paludarium|Plants</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Terrarium Moss|Mosses</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Terrarium &amp; Paludarium|Plants</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Terrarium Moss|Mosses</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -14069,12 +14069,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
     </row>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
     </row>
@@ -14120,12 +14120,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Terrarium &amp; Paludarium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Terrarium Moss</t>
         </is>
       </c>
     </row>
@@ -14137,12 +14137,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brand &amp; Specialized</t>
+          <t>Plants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DOOA System</t>
+          <t>Rare &amp; Exotic</t>
         </is>
       </c>
     </row>
@@ -14154,12 +14154,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aquascaping</t>
+          <t>Plants</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Starter Packs</t>
+          <t>Aquatic Plants</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Terrarium Accessories</t>
+          <t>Terrarium Plants</t>
         </is>
       </c>
     </row>
